--- a/_static/files/calculations_constraints_matrix/calculations_constraints_matrix.xlsx
+++ b/_static/files/calculations_constraints_matrix/calculations_constraints_matrix.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10609"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/garethbestor/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36B2B851-8344-41F7-B909-7B68AE20E722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87CA60AA-2B10-B54B-B70C-05EF3A0E3D46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3435" yWindow="645" windowWidth="15945" windowHeight="11685" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3440" yWindow="640" windowWidth="33500" windowHeight="22400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="80">
   <si>
     <t>type</t>
   </si>
@@ -71,21 +71,6 @@
     <t>end_group</t>
   </si>
   <si>
-    <t>##### 0-14 Years</t>
-  </si>
-  <si>
-    <t>w1 no-label</t>
-  </si>
-  <si>
-    <t>##### 15-64 Years</t>
-  </si>
-  <si>
-    <t>##### 65+ Years</t>
-  </si>
-  <si>
-    <t>##### Total (Column)</t>
-  </si>
-  <si>
     <t>form_title</t>
   </si>
   <si>
@@ -264,6 +249,18 @@
   </si>
   <si>
     <t>Your input now exceeds the total HH members!</t>
+  </si>
+  <si>
+    <t>**0-14 Years**</t>
+  </si>
+  <si>
+    <t>**15-64 Years**</t>
+  </si>
+  <si>
+    <t>**65+ Years**</t>
+  </si>
+  <si>
+    <t>**Total (Column)**</t>
   </si>
 </sst>
 </file>
@@ -287,7 +284,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -306,6 +303,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -319,25 +322,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -357,9 +366,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -397,9 +406,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -432,26 +441,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -484,26 +476,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -678,55 +653,55 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="49.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="58.140625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="60.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="43.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="1"/>
+    <col min="3" max="3" width="41.83203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="51.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="52.5" style="1" customWidth="1"/>
+    <col min="8" max="8" width="37.1640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="9.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.1640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G1" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -734,47 +709,38 @@
       <c r="D2" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="F2" s="4"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="4"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="4"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>12</v>
@@ -782,16 +748,13 @@
       <c r="E5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>13</v>
@@ -799,16 +762,13 @@
       <c r="E6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="4"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>14</v>
@@ -816,455 +776,395 @@
       <c r="E7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="4"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="4"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+    </row>
+    <row r="9" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" s="1" t="s">
+      <c r="B9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="4"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D11" s="1" t="b">
         <v>1</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11" s="4"/>
-      <c r="G11" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D12" s="1" t="b">
         <v>1</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F12" s="4"/>
-      <c r="G12" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
+        <v>11</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="I13" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F14" s="4"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+    </row>
+    <row r="15" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E15" s="1" t="s">
+      <c r="B15" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F15" s="4"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F16" s="4"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D17" s="1" t="b">
         <v>1</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F17" s="4"/>
-      <c r="G17" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="H17" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="H17" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D18" s="1" t="b">
         <v>1</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F18" s="4"/>
-      <c r="G18" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
+        <v>11</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="I19" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F20" s="4"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+    </row>
+    <row r="21" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E21" s="1" t="s">
+      <c r="B21" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E21" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F21" s="4"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>19</v>
+        <v>78</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F22" s="4"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D23" s="1" t="b">
         <v>1</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F23" s="4"/>
-      <c r="G23" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D24" s="1" t="b">
         <v>1</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F24" s="4"/>
-      <c r="G24" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
+        <v>11</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="I25" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F26" s="4"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="6"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
+    </row>
+    <row r="27" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E27" s="1" t="s">
+      <c r="B27" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E27" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F27" s="4"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F28" s="4"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D29" s="1" t="b">
         <v>1</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
+        <v>11</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="I29" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D30" s="1" t="b">
         <v>1</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
+        <v>11</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="I30" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
+        <v>11</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="I31" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F32" s="4"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1273,29 +1173,32 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="77.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="66.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.1640625" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.1640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>24</v>
-      </c>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G22" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
